--- a/data/generated/nvda.xlsx
+++ b/data/generated/nvda.xlsx
@@ -136,7 +136,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Refreshed from Yahoo Finance NVDA monthly history on 2026-03-11 01:26:25.
+        <t>Refreshed from Yahoo Finance NVDA monthly history on 2026-03-11 01:30:59.
 https://finance.yahoo.com/quote/NVDA/history/
 Earliest reliable live month for this series: 2010-06-01.</t>
       </text>

--- a/data/generated/nvda.xlsx
+++ b/data/generated/nvda.xlsx
@@ -136,7 +136,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Refreshed from Yahoo Finance NVDA monthly history on 2026-03-11 01:30:59.
+        <t>Refreshed from Yahoo Finance NVDA monthly history on 2026-03-11 01:35:44.
 https://finance.yahoo.com/quote/NVDA/history/
 Earliest reliable live month for this series: 2010-06-01.</t>
       </text>
